--- a/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p2.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p2.xlsx
@@ -816,16 +816,16 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F2">
-        <v>0.7407407407407408</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.6999999999999998</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J2">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -848,16 +848,16 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3">
-        <v>0.6666666666666666</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="J3">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -886,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="F4">
-        <v>0.5555555555555556</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -898,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.7333333333333334</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0.8148148148148149</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -930,10 +930,10 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J5">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -944,10 +944,10 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0.4000000000000001</v>
@@ -956,16 +956,16 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -994,10 +994,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.6</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="J7">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1020,10 +1020,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I8">
         <v>0.4000000000000001</v>
@@ -1052,13 +1052,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0.8571428571428571</v>
@@ -1072,25 +1072,25 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.4333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>0.6190476190476191</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I10">
-        <v>0.6</v>
+        <v>0.7714285714285714</v>
       </c>
       <c r="J10">
         <v>0.8571428571428571</v>
@@ -1116,13 +1116,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0.8333333333333334</v>
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J12">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1186,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J13">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1206,10 +1206,10 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F14">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J14">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1238,10 +1238,10 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F15">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0.5333333333333333</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J15">
-        <v>0.6666666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1264,16 +1264,16 @@
         <v>24</v>
       </c>
       <c r="C16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F16">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J16">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1296,25 +1296,25 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I17">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="J17">
         <v>0.8333333333333334</v>
@@ -1334,16 +1334,16 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="F18">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I18">
         <v>0.6</v>
@@ -1360,28 +1360,28 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E19">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F19">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G19">
-        <v>0.2</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H19">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I19">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1392,28 +1392,28 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F20">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I20">
-        <v>0.6999999999999998</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J20">
-        <v>0.875</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1430,22 +1430,22 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F21">
+        <v>0.75</v>
+      </c>
+      <c r="G21">
+        <v>0.25</v>
+      </c>
+      <c r="H21">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
         <v>0.625</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0.6</v>
-      </c>
-      <c r="J21">
-        <v>0.75</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1456,28 +1456,28 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D22">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F22">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I22">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J22">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1488,16 +1488,16 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E23">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F23">
-        <v>0.8333333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0.6999999999999998</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="J23">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0.6999999999999998</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="J24">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1552,28 +1552,28 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J25">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1590,16 +1590,16 @@
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F26">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I26">
         <v>0.6</v>
@@ -1616,28 +1616,28 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F27">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J27">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1666,10 +1666,10 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J28">
-        <v>0.625</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1686,22 +1686,22 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F29">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J29">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1712,28 +1712,28 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F30">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I30">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J30">
-        <v>0.625</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1750,22 +1750,22 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F31">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J31">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1776,7 +1776,7 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1788,16 +1788,16 @@
         <v>0.75</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J32">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1820,16 +1820,16 @@
         <v>0.75</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J33">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1840,22 +1840,22 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0.4333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F34">
-        <v>0.5416666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I34">
         <v>0.6</v>
@@ -1878,22 +1878,22 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F35">
-        <v>0.5833333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I35">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J35">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1904,16 +1904,16 @@
         <v>44</v>
       </c>
       <c r="C36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E36">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F36">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0.6</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J36">
         <v>0.75</v>
@@ -1942,22 +1942,22 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J38">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2006,22 +2006,22 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F39">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J39">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2044,16 +2044,16 @@
         <v>0.75</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J40">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2064,7 +2064,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2076,16 +2076,16 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J41">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2108,16 +2108,16 @@
         <v>0.75</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J42">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2134,22 +2134,22 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F43">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J43">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2166,22 +2166,22 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F44">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44">
-        <v>0.5</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J44">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2198,22 +2198,22 @@
         <v>1</v>
       </c>
       <c r="E45">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F45">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I45">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J45">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2224,28 +2224,28 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F46">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I46">
-        <v>0.7259259259259259</v>
+        <v>0.5</v>
       </c>
       <c r="J46">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -2256,28 +2256,28 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E47">
-        <v>0.4000000000000001</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F47">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J47">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -2288,28 +2288,28 @@
         <v>56</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F48">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J48">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -2320,28 +2320,28 @@
         <v>57</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F49">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0.6666666666666666</v>
       </c>
       <c r="J49">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2352,28 +2352,28 @@
         <v>58</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F50">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J50">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2390,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F51">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2402,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J51">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2416,10 +2416,10 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E52">
         <v>0.6</v>
@@ -2428,16 +2428,16 @@
         <v>0.75</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0.6666666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J52">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2454,22 +2454,22 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>0.4666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>0.5833333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0.6666666666666666</v>
       </c>
       <c r="J53">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2483,25 +2483,25 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E54">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F54">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G54">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J54">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F55">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -2547,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E56">
         <v>0.6</v>
@@ -2556,16 +2556,16 @@
         <v>0.75</v>
       </c>
       <c r="G56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J56">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2588,16 +2588,16 @@
         <v>0.75</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I57">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J57">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2614,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>0.6111111111111112</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F58">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2646,10 +2646,10 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>0.5</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F59">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2658,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="J59">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2672,10 +2672,10 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D60">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E60">
         <v>0.5</v>
@@ -2684,16 +2684,16 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="G60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>0.6</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="J60">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2710,22 +2710,22 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F61">
+        <v>0.8095238095238094</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0.5</v>
+      </c>
+      <c r="J61">
         <v>0.7142857142857143</v>
-      </c>
-      <c r="G61">
-        <v>0.5</v>
-      </c>
-      <c r="H61">
-        <v>0.5</v>
-      </c>
-      <c r="I61">
-        <v>0.6</v>
-      </c>
-      <c r="J61">
-        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2742,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="J62">
         <v>0.5555555555555556</v>
@@ -2768,25 +2768,25 @@
         <v>71</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0.4000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="F63">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>0.6</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="J63">
         <v>0.8571428571428571</v>
@@ -2806,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>0.6</v>
+        <v>0.8214285714285715</v>
       </c>
       <c r="J64">
         <v>0.8571428571428571</v>
@@ -2832,16 +2832,16 @@
         <v>73</v>
       </c>
       <c r="C65">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F65">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2850,10 +2850,10 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J65">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2864,28 +2864,28 @@
         <v>74</v>
       </c>
       <c r="C66">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="D66">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E66">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J66">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2896,22 +2896,22 @@
         <v>75</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F67">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0.6</v>
@@ -2934,22 +2934,22 @@
         <v>0.5</v>
       </c>
       <c r="E68">
-        <v>0.4000000000000001</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F68">
-        <v>0.5714285714285714</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>0.6</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J68">
-        <v>0.8571428571428571</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2960,10 +2960,10 @@
         <v>77</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="D69">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E69">
         <v>0.5</v>
@@ -2972,10 +2972,10 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I69">
         <v>0.5</v>
@@ -2992,10 +2992,10 @@
         <v>78</v>
       </c>
       <c r="C70">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E70">
         <v>0.5</v>
@@ -3004,13 +3004,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I70">
-        <v>0.5</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="J70">
         <v>0.8333333333333334</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3056,25 +3056,25 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F72">
         <v>0.8333333333333334</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72">
-        <v>0.5</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="J72">
         <v>0.8333333333333334</v>
@@ -3094,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F73">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3106,10 +3106,10 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J73">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>0.5666666666666667</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F74">
-        <v>0.7083333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3138,10 +3138,10 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J74">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -3158,22 +3158,22 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>0.4000000000000001</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F75">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>0.6</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="J75">
-        <v>0.8571428571428571</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -3190,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J76">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -3222,10 +3222,10 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>0.5666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="F77">
-        <v>0.7083333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -3234,10 +3234,10 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J77">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -3254,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F78">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3266,10 +3266,10 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>0.7259259259259259</v>
+        <v>0.6</v>
       </c>
       <c r="J78">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -3280,16 +3280,16 @@
         <v>87</v>
       </c>
       <c r="C79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F79">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0.7259259259259259</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J79">
         <v>0.875</v>
@@ -3318,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F80">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -3350,10 +3350,10 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F81">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -3376,22 +3376,22 @@
         <v>90</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E82">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F82">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I82">
         <v>0.6999999999999998</v>
@@ -3408,7 +3408,7 @@
         <v>91</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3440,7 +3440,7 @@
         <v>92</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3458,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J84">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3472,28 +3472,28 @@
         <v>93</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F85">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J85">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3504,28 +3504,28 @@
         <v>94</v>
       </c>
       <c r="C86">
-        <v>0.7777777777777777</v>
+        <v>0.5</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E86">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F86">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I86">
-        <v>0.6999999999999998</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J86">
-        <v>0.875</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.5666666666666667</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F87">
-        <v>0.7083333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3554,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0.6666666666666666</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J87">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3574,22 +3574,22 @@
         <v>1</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F88">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J88">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -3600,16 +3600,16 @@
         <v>97</v>
       </c>
       <c r="C89">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F89">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -3618,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>0.6999999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="J89">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3638,10 +3638,10 @@
         <v>1</v>
       </c>
       <c r="E90">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F90">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -3650,10 +3650,10 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J90">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3670,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0.5333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F91">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -3699,25 +3699,25 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E92">
-        <v>0.5333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F92">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="G92">
         <v>0.3333333333333333</v>
       </c>
       <c r="H92">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I92">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J92">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3760,28 +3760,28 @@
         <v>102</v>
       </c>
       <c r="C94">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="D94">
+        <v>0.5</v>
+      </c>
+      <c r="E94">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="F94">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G94">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D94">
-        <v>0.5</v>
-      </c>
-      <c r="E94">
-        <v>0.5</v>
-      </c>
-      <c r="F94">
-        <v>0.625</v>
-      </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
       <c r="H94">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I94">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="J94">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3792,28 +3792,28 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>0.4000000000000001</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F95">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>0.2777777777777777</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I95">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="J95">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3824,28 +3824,28 @@
         <v>104</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="F96">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G96">
+        <v>0.5</v>
+      </c>
+      <c r="H96">
+        <v>0.5</v>
+      </c>
+      <c r="I96">
         <v>0.5666666666666667</v>
       </c>
-      <c r="F96">
+      <c r="J96">
         <v>0.7083333333333334</v>
-      </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
-        <v>0.6</v>
-      </c>
-      <c r="J96">
-        <v>0.75</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3862,16 +3862,16 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0.4000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F97">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
         <v>0.6</v>
@@ -3888,22 +3888,22 @@
         <v>106</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F98">
-        <v>0.625</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I98">
         <v>0.6</v>
@@ -3926,22 +3926,22 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F99">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J99">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3958,13 +3958,13 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F100">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3996,13 +3996,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I101">
-        <v>0.5185185185185185</v>
+        <v>0.5</v>
       </c>
       <c r="J101">
         <v>0.8333333333333334</v>
@@ -4131,19 +4131,19 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>0.7072222222222223</v>
+        <v>0.7672460317460319</v>
       </c>
       <c r="C2">
-        <v>0.1336666666666667</v>
+        <v>0.355111111111111</v>
       </c>
       <c r="D2">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4151,19 +4151,19 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>0.715</v>
+        <v>0.7883333333333333</v>
       </c>
       <c r="C3">
-        <v>0.1475</v>
+        <v>0.3808333333333334</v>
       </c>
       <c r="D3">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4171,19 +4171,19 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>0.5337777777777777</v>
+        <v>0.5969259259259259</v>
       </c>
       <c r="C4">
-        <v>0.6144074074074074</v>
+        <v>0.6511865079365079</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4191,19 +4191,19 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>0.6837367724867724</v>
+        <v>0.767063492063492</v>
       </c>
       <c r="C5">
-        <v>0.7806481481481481</v>
+        <v>0.8038624338624338</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4244,22 +4244,22 @@
         <v>116</v>
       </c>
       <c r="B2">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4267,22 +4267,22 @@
         <v>117</v>
       </c>
       <c r="B3">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4290,22 +4290,22 @@
         <v>118</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4313,22 +4313,22 @@
         <v>119</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
